--- a/data/trans_camb/IP16A06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Edad-trans_camb.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,0</t>
+          <t>-6,89; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,0</t>
+          <t>-7,76; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,95</t>
+          <t>-2,94; 0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,0</t>
+          <t>-4,28; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 0,0</t>
+          <t>-13,64; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 0,0</t>
+          <t>-13,64; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 0,0</t>
+          <t>-18,97; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 0,0</t>
+          <t>-17,52; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,03; -1,18</t>
+          <t>-10,12; -1,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; -1,18</t>
+          <t>-10,99; -1,17</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 11,23</t>
+          <t>-7,84; 10,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 4,73</t>
+          <t>-10,66; 4,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 14,93</t>
+          <t>-2,48; 16,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 11,47</t>
+          <t>-4,81; 11,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 10,37</t>
+          <t>-1,95; 10,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,71</t>
+          <t>-5,17; 4,79</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 807,63</t>
+          <t>-53,04; 693,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,16; 340,14</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,06</t>
+          <t>-2,84; 2,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,64</t>
+          <t>-3,56; 0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,25</t>
+          <t>-3,45; 1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,18</t>
+          <t>-3,64; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,24</t>
+          <t>-2,32; 1,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,4</t>
+          <t>-2,72; 0,47</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,66; 184,84</t>
+          <t>-89,82; 174,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,65</t>
+          <t>-99,03; 273,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 148,45</t>
+          <t>-75,65; 113,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,76; 71,15</t>
+          <t>-88,57; 74,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Edad-trans_camb.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 0,0</t>
+          <t>-6,92; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,0</t>
+          <t>-6,92; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,94</t>
+          <t>-2,96; 0,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 0,0</t>
+          <t>-3,73; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 0,0</t>
+          <t>-14,58; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 0,0</t>
+          <t>-14,57; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 0,0</t>
+          <t>-17,47; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 0,0</t>
+          <t>-20,03; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -1,18</t>
+          <t>-10,81; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -1,17</t>
+          <t>-10,91; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 10,69</t>
+          <t>-6,77; 11,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 4,66</t>
+          <t>-10,71; 4,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 16,74</t>
+          <t>-2,31; 16,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 11,58</t>
+          <t>-4,65; 10,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 10,01</t>
+          <t>-2,4; 10,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,79</t>
+          <t>-5,77; 4,77</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 693,87</t>
+          <t>-58,13; 880,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 433,2</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,12</t>
+          <t>-2,6; 2,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,87</t>
+          <t>-3,48; 0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,31</t>
+          <t>-3,52; 1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,16</t>
+          <t>-3,68; 1,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,08</t>
+          <t>-2,27; 1,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,47</t>
+          <t>-2,77; 0,39</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-89,82; 174,06</t>
+          <t>-90,89; 192,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-99,03; 273,95</t>
+          <t>-100,0; 215,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 113,53</t>
+          <t>-75,71; 118,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 74,59</t>
+          <t>-90,74; 48,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Edad-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,37</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>-6,97; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,12; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,0</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,96</t>
+          <t>-2,96; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,0</t>
+          <t>-4,06; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-2,9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-2,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 0,0</t>
+          <t>-16,15; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 0,0</t>
+          <t>-15,67; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 0,0</t>
+          <t>-14,91; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 0,0</t>
+          <t>-14,9; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 0,0</t>
+          <t>-11,03; -1,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 0,0</t>
+          <t>-11,58; -1,18</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-1,4</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 11,56</t>
+          <t>-2,17; 14,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 4,94</t>
+          <t>-4,73; 11,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 16,04</t>
+          <t>-8,0; 11,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 10,97</t>
+          <t>-11,53; 4,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 10,72</t>
+          <t>-2,57; 10,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,77</t>
+          <t>-5,69; 4,71</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>161,53%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>43,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-30,77%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>161,53%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 880,71</t>
+          <t>-53,03; 807,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 433,2</t>
+          <t>-89,16; 340,14</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,84</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,31</t>
+          <t>-3,32; 1,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,71</t>
+          <t>-3,76; 1,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,31</t>
+          <t>-2,76; 2,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,2</t>
+          <t>-3,7; 0,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,17</t>
+          <t>-2,28; 1,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,39</t>
+          <t>-2,65; 0,4</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-37,62%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-43,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-3,31%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-56,94%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-37,62%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-43,78%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,66; 184,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 240,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,89; 192,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 118,14</t>
+          <t>-74,77; 148,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-90,74; 48,05</t>
+          <t>-87,76; 71,15</t>
         </is>
       </c>
     </row>
